--- a/artfynd/A 30637-2022 artfynd.xlsx
+++ b/artfynd/A 30637-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30637-2022 artfynd.xlsx
+++ b/artfynd/A 30637-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89120359</v>
+        <v>89120383</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>535</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517564.8331265045</v>
+        <v>517594</v>
       </c>
       <c r="R2" t="n">
-        <v>6491414.204441611</v>
+        <v>6491490</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>89120395</v>
       </c>
       <c r="B3" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +787,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517594.0660332762</v>
+        <v>517594</v>
       </c>
       <c r="R3" t="n">
-        <v>6491537.972309281</v>
+        <v>6491538</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89120362</v>
+        <v>89120359</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517610.9917800366</v>
+        <v>517565</v>
       </c>
       <c r="R4" t="n">
-        <v>6491493.185206305</v>
+        <v>6491414</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89120383</v>
+        <v>89120362</v>
       </c>
       <c r="B5" t="n">
-        <v>93372</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>535</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517593.7595550436</v>
+        <v>517611</v>
       </c>
       <c r="R5" t="n">
-        <v>6491489.977542517</v>
+        <v>6491493</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89120500</v>
+        <v>89120363</v>
       </c>
       <c r="B6" t="n">
-        <v>86134</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4377</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517589.866364995</v>
+        <v>517564</v>
       </c>
       <c r="R6" t="n">
-        <v>6491542.126708104</v>
+        <v>6491601</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89120363</v>
+        <v>89120500</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4377</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517563.9934910889</v>
+        <v>517590</v>
       </c>
       <c r="R7" t="n">
-        <v>6491600.95782977</v>
+        <v>6491542</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,12 +1260,7 @@
         <v>89120437</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517556.7403694628</v>
+        <v>517557</v>
       </c>
       <c r="R8" t="n">
-        <v>6491586.840499321</v>
+        <v>6491587</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1325,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,12 +1357,7 @@
         <v>89120438</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517560.8578830209</v>
+        <v>517561</v>
       </c>
       <c r="R9" t="n">
-        <v>6491600.943733339</v>
+        <v>6491601</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1532,19 +1422,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,12 +1454,7 @@
         <v>89120495</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517618.9348578512</v>
+        <v>517619</v>
       </c>
       <c r="R10" t="n">
-        <v>6491586.077188631</v>
+        <v>6491586</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,19 +1519,9 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-11-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,6 +1545,107 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>88182982</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Juteberget, Borensberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>517654</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6491512</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunneby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Brunosson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Brunosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
